--- a/data/satisfaction_detail/2026/1-8月/婚宴.xlsx
+++ b/data/satisfaction_detail/2026/1-8月/婚宴.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>9.471248630887187</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.76</v>
+        <v>9.879167579408543</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.69</v>
+        <v>9.775520262869659</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>9.880000000000001</v>
+        <v>9.916089813800657</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.33</v>
+        <v>9.6</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.67</v>
+        <v>9.799999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -511,10 +511,10 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.43</v>
+        <v>9.544578313253011</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.85</v>
+        <v>9.873493975903614</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +524,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.466933187294632</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.887294633077765</v>
       </c>
     </row>
     <row r="7">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.884994523548739</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.93</v>
+        <v>9.935596933187293</v>
       </c>
     </row>
     <row r="8">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.484249726177437</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.85</v>
+        <v>9.843658269441402</v>
       </c>
     </row>
     <row r="9">
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.81</v>
+        <v>9.838828039430448</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.94</v>
+        <v>9.953997809419494</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.91</v>
+        <v>9.935596933187293</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.924096385542168</v>
       </c>
     </row>
     <row r="11">
@@ -589,10 +589,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>9.91</v>
+        <v>9.935596933187293</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.9</v>
+        <v>9.933296823658269</v>
       </c>
     </row>
     <row r="12">
@@ -602,10 +602,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>9.98</v>
+        <v>9.979299014238773</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10</v>
+        <v>9.999999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.85</v>
+        <v>9.866593647316538</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.91</v>
+        <v>9.928696604600217</v>
       </c>
     </row>
     <row r="14">
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.795290251916756</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.898795180722891</v>
       </c>
     </row>
     <row r="15">
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>9.07</v>
+        <v>9.161577217962758</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.834852135815991</v>
       </c>
     </row>
     <row r="16">
@@ -654,10 +654,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>7.82</v>
+        <v>7.622222222222222</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8.91</v>
+        <v>9.533333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>9.667042716319825</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.81</v>
+        <v>9.838992332968235</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9</v>
+        <v>9.027338444687841</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.92</v>
+        <v>9.928696604600217</v>
       </c>
     </row>
     <row r="19">
@@ -693,10 +693,10 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.81</v>
+        <v>9.800613362541073</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.92</v>
+        <v>9.927776560788608</v>
       </c>
     </row>
     <row r="20">
